--- a/data/excel/statements.xlsx
+++ b/data/excel/statements.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H223"/>
+  <dimension ref="A1:H224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-08-12T20:21:14+00:00</t>
+          <t>2026-10-26T07:10:13+00:00</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -8518,11 +8518,11 @@
 The Committee seeks to achieve maximum employment and inflation at the rate of 2 percent over the longer run. In support of these goals, the Committee decided to raise the target range for the federal funds rate to 3-3/4 to 4 percent. The Committee anticipates that ongoing increases in the target range will be appropriate in order to attain a stance of monetary policy that is sufficiently restrictive to return inflation to 2 percent over time. In determining the pace of future increases in the target range, the Committee will take into account the cumulative tightening of monetary policy, the lags with which monetary policy affects economic activity and inflation, and economic and financial developments. In addition, the Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgage-backed securities, as described in the Plans for Reducing the Size of the Federal Reserve's Balance Sheet that were issued in May. The Committee is strongly committed to returning inflation to its 2 percent objective.
 In assessing the appropriate stance of monetary policy, the Committee will continue to monitor the implications of incoming information for the economic outlook. The Committee would be prepared to adjust the stance of monetary policy as appropriate if risks emerge that could impede the attainment of the Committee's goals. The Committee's assessments will take into account a wide range of information, including readings on public health, labor market conditions, inflation pressures and inflation expectations, and financial and international developments.
 Voting for the monetary policy action were Jerome H. Powell, Chair; John C. Williams, Vice Chair; Michael S. Barr; Michelle W. Bowman; Lael Brainard; James Bullard; Susan M. Collins; Lisa D. Cook; Esther L. George; Philip N. Jefferson; Loretta J. Mester; and Christopher J. Waller.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G193" t="n">
-        <v>2594</v>
+        <v>2590</v>
       </c>
       <c r="H193" t="inlineStr"/>
     </row>
@@ -8549,7 +8549,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-08-12T20:21:21+00:00</t>
+          <t>2026-10-26T07:10:14+00:00</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -8561,11 +8561,11 @@
 The Committee seeks to achieve maximum employment and inflation at the rate of 2 percent over the longer run. In support of these goals, the Committee decided to raise the target range for the federal funds rate to 4-1/4 to 4-1/2 percent. The Committee anticipates that ongoing increases in the target range will be appropriate in order to attain a stance of monetary policy that is sufficiently restrictive to return inflation to 2 percent over time. In determining the pace of future increases in the target range, the Committee will take into account the cumulative tightening of monetary policy, the lags with which monetary policy affects economic activity and inflation, and economic and financial developments. In addition, the Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgage-backed securities, as described in the Plans for Reducing the Size of the Federal Reserve's Balance Sheet that were issued in May. The Committee is strongly committed to returning inflation to its 2 percent objective.
 In assessing the appropriate stance of monetary policy, the Committee will continue to monitor the implications of incoming information for the economic outlook. The Committee would be prepared to adjust the stance of monetary policy as appropriate if risks emerge that could impede the attainment of the Committee's goals. The Committee's assessments will take into account a wide range of information, including readings on public health, labor market conditions, inflation pressures and inflation expectations, and financial and international developments.
 Voting for the monetary policy action were Jerome H. Powell, Chair; John C. Williams, Vice Chair; Michael S. Barr; Michelle W. Bowman; Lael Brainard; James Bullard; Susan M. Collins; Lisa D. Cook; Esther L. George; Philip N. Jefferson; Loretta J. Mester; and Christopher J. Waller.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G194" t="n">
-        <v>2594</v>
+        <v>2590</v>
       </c>
       <c r="H194" t="inlineStr"/>
     </row>
@@ -8592,7 +8592,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-08-12T20:21:28+00:00</t>
+          <t>2026-10-26T07:10:15+00:00</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -8604,11 +8604,11 @@
 The Committee seeks to achieve maximum employment and inflation at the rate of 2 percent over the longer run. In support of these goals, the Committee decided to raise the target range for the federal funds rate to 4-1/2 to 4-3/4 percent. The Committee anticipates that ongoing increases in the target range will be appropriate in order to attain a stance of monetary policy that is sufficiently restrictive to return inflation to 2 percent over time. In determining the extent of future increases in the target range, the Committee will take into account the cumulative tightening of monetary policy, the lags with which monetary policy affects economic activity and inflation, and economic and financial developments. In addition, the Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgage-backed securities, as described in its previously announced plans. The Committee is strongly committed to returning inflation to its 2 percent objective.
 In assessing the appropriate stance of monetary policy, the Committee will continue to monitor the implications of incoming information for the economic outlook. The Committee would be prepared to adjust the stance of monetary policy as appropriate if risks emerge that could impede the attainment of the Committee's goals. The Committee's assessments will take into account a wide range of information, including readings on labor market conditions, inflation pressures and inflation expectations, and financial and international developments.
 Voting for the monetary policy action were Jerome H. Powell, Chair; John C. Williams, Vice Chair; Michael S. Barr; Michelle W. Bowman; Lael Brainard; Lisa D. Cook; Austan D. Goolsbee; Patrick Harker; Philip N. Jefferson; Neel Kashkari; Lorie K. Logan; and Christopher J. Waller.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G195" t="n">
-        <v>2341</v>
+        <v>2337</v>
       </c>
       <c r="H195" t="inlineStr"/>
     </row>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2026-08-12T20:21:36+00:00</t>
+          <t>2026-10-26T07:10:16+00:00</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -8647,11 +8647,11 @@
 The Committee seeks to achieve maximum employment and inflation at the rate of 2 percent over the longer run. In support of these goals, the Committee decided to raise the target range for the federal funds rate to 4-3/4 to 5 percent. The Committee will closely monitor incoming information and assess the implications for monetary policy. The Committee anticipates that some additional policy firming may be appropriate in order to attain a stance of monetary policy that is sufficiently restrictive to return inflation to 2 percent over time. In determining the extent of future increases in the target range, the Committee will take into account the cumulative tightening of monetary policy, the lags with which monetary policy affects economic activity and inflation, and economic and financial developments. In addition, the Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgage-backed securities, as described in its previously announced plans. The Committee is strongly committed to returning inflation to its 2 percent objective.
 In assessing the appropriate stance of monetary policy, the Committee will continue to monitor the implications of incoming information for the economic outlook. The Committee would be prepared to adjust the stance of monetary policy as appropriate if risks emerge that could impede the attainment of the Committee's goals. The Committee's assessments will take into account a wide range of information, including readings on labor market conditions, inflation pressures and inflation expectations, and financial and international developments.
 Voting for the monetary policy action were Jerome H. Powell, Chair; John C. Williams, Vice Chair; Michael S. Barr; Michelle W. Bowman; Lisa D. Cook; Austan D. Goolsbee; Patrick Harker; Philip N. Jefferson; Neel Kashkari; Lorie K. Logan; and Christopher J. Waller.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G196" t="n">
-        <v>2542</v>
+        <v>2538</v>
       </c>
       <c r="H196" t="inlineStr"/>
     </row>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-08-12T20:21:43+00:00</t>
+          <t>2026-10-26T07:10:17+00:00</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -8690,11 +8690,11 @@
 The Committee seeks to achieve maximum employment and inflation at the rate of 2 percent over the longer run. In support of these goals, the Committee decided to raise the target range for the federal funds rate to 5 to 5-1/4 percent. The Committee will closely monitor incoming information and assess the implications for monetary policy. In determining the extent to which additional policy firming may be appropriate to return inflation to 2 percent over time, the Committee will take into account the cumulative tightening of monetary policy, the lags with which monetary policy affects economic activity and inflation, and economic and financial developments. In addition, the Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgage-backed securities, as described in its previously announced plans. The Committee is strongly committed to returning inflation to its 2 percent objective.
 In assessing the appropriate stance of monetary policy, the Committee will continue to monitor the implications of incoming information for the economic outlook. The Committee would be prepared to adjust the stance of monetary policy as appropriate if risks emerge that could impede the attainment of the Committee's goals. The Committee's assessments will take into account a wide range of information, including readings on labor market conditions, inflation pressures and inflation expectations, and financial and international developments.
 Voting for the monetary policy action were Jerome H. Powell, Chair; John C. Williams, Vice Chair; Michael S. Barr; Michelle W. Bowman; Lisa D. Cook; Austan D. Goolsbee; Patrick Harker; Philip N. Jefferson; Neel Kashkari; Lorie K. Logan; and Christopher J. Waller.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G197" t="n">
-        <v>2330</v>
+        <v>2326</v>
       </c>
       <c r="H197" t="inlineStr"/>
     </row>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-08-12T20:21:51+00:00</t>
+          <t>2026-10-26T07:10:18+00:00</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -8733,11 +8733,11 @@
 The Committee seeks to achieve maximum employment and inflation at the rate of 2 percent over the longer run. In support of these goals, the Committee decided to maintain the target range for the federal funds rate at 5 to 5-1/4 percent. Holding the target range steady at this meeting allows the Committee to assess additional information and its implications for monetary policy. In determining the extent of additional policy firming that may be appropriate to return inflation to 2 percent over time, the Committee will take into account the cumulative tightening of monetary policy, the lags with which monetary policy affects economic activity and inflation, and economic and financial developments. In addition, the Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgage-backed securities, as described in its previously announced plans. The Committee is strongly committed to returning inflation to its 2 percent objective.
 In assessing the appropriate stance of monetary policy, the Committee will continue to monitor the implications of incoming information for the economic outlook. The Committee would be prepared to adjust the stance of monetary policy as appropriate if risks emerge that could impede the attainment of the Committee's goals. The Committee's assessments will take into account a wide range of information, including readings on labor market conditions, inflation pressures and inflation expectations, and financial and international developments.
 Voting for the monetary policy action were Jerome H. Powell, Chair; John C. Williams, Vice Chair; Michael S. Barr; Michelle W. Bowman; Lisa D. Cook; Austan D. Goolsbee; Patrick Harker; Philip N. Jefferson; Neel Kashkari; Lorie K. Logan; and Christopher J. Waller.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G198" t="n">
-        <v>2397</v>
+        <v>2393</v>
       </c>
       <c r="H198" t="inlineStr"/>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-08-12T20:21:58+00:00</t>
+          <t>2026-10-26T07:10:19+00:00</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -8776,11 +8776,11 @@
 The Committee seeks to achieve maximum employment and inflation at the rate of 2 percent over the longer run. In support of these goals, the Committee decided to raise the target range for the federal funds rate to 5-1/4 to 5-1/2 percent. The Committee will continue to assess additional information and its implications for monetary policy. In determining the extent of additional policy firming that may be appropriate to return inflation to 2 percent over time, the Committee will take into account the cumulative tightening of monetary policy, the lags with which monetary policy affects economic activity and inflation, and economic and financial developments. In addition, the Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgage-backed securities, as described in its previously announced plans. The Committee is strongly committed to returning inflation to its 2 percent objective.
 In assessing the appropriate stance of monetary policy, the Committee will continue to monitor the implications of incoming information for the economic outlook. The Committee would be prepared to adjust the stance of monetary policy as appropriate if risks emerge that could impede the attainment of the Committee's goals. The Committee's assessments will take into account a wide range of information, including readings on labor market conditions, inflation pressures and inflation expectations, and financial and international developments.
 Voting for the monetary policy action were Jerome H. Powell, Chair; John C. Williams, Vice Chair; Michael S. Barr; Michelle W. Bowman; Lisa D. Cook; Austan D. Goolsbee; Patrick Harker; Philip N. Jefferson; Neel Kashkari; Lorie K. Logan; and Christopher J. Waller.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G199" t="n">
-        <v>2354</v>
+        <v>2350</v>
       </c>
       <c r="H199" t="inlineStr"/>
     </row>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2026-08-12T20:22:07+00:00</t>
+          <t>2026-10-26T07:10:20+00:00</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -8819,11 +8819,11 @@
 The Committee seeks to achieve maximum employment and inflation at the rate of 2 percent over the longer run. In support of these goals, the Committee decided to maintain the target range for the federal funds rate at 5-1/4 to 5-1/2 percent. The Committee will continue to assess additional information and its implications for monetary policy. In determining the extent of additional policy firming that may be appropriate to return inflation to 2 percent over time, the Committee will take into account the cumulative tightening of monetary policy, the lags with which monetary policy affects economic activity and inflation, and economic and financial developments. In addition, the Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgage-backed securities, as described in its previously announced plans. The Committee is strongly committed to returning inflation to its 2 percent objective.
 In assessing the appropriate stance of monetary policy, the Committee will continue to monitor the implications of incoming information for the economic outlook. The Committee would be prepared to adjust the stance of monetary policy as appropriate if risks emerge that could impede the attainment of the Committee's goals. The Committee's assessments will take into account a wide range of information, including readings on labor market conditions, inflation pressures and inflation expectations, and financial and international developments.
 Voting for the monetary policy action were Jerome H. Powell, Chair; John C. Williams, Vice Chair; Michael S. Barr; Michelle W. Bowman; Lisa D. Cook; Austan D. Goolsbee; Patrick Harker; Philip N. Jefferson; Neel Kashkari; Adriana D. Kugler; Lorie K. Logan; and Christopher J. Waller.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G200" t="n">
-        <v>2391</v>
+        <v>2387</v>
       </c>
       <c r="H200" t="inlineStr"/>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-08-12T20:22:15+00:00</t>
+          <t>2026-10-26T07:10:21+00:00</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -8862,11 +8862,11 @@
 The Committee seeks to achieve maximum employment and inflation at the rate of 2 percent over the longer run. In support of these goals, the Committee decided to maintain the target range for the federal funds rate at 5-1/4 to 5-1/2 percent. The Committee will continue to assess additional information and its implications for monetary policy. In determining the extent of additional policy firming that may be appropriate to return inflation to 2 percent over time, the Committee will take into account the cumulative tightening of monetary policy, the lags with which monetary policy affects economic activity and inflation, and economic and financial developments. In addition, the Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgage-backed securities, as described in its previously announced plans. The Committee is strongly committed to returning inflation to its 2 percent objective.
 In assessing the appropriate stance of monetary policy, the Committee will continue to monitor the implications of incoming information for the economic outlook. The Committee would be prepared to adjust the stance of monetary policy as appropriate if risks emerge that could impede the attainment of the Committee's goals. The Committee's assessments will take into account a wide range of information, including readings on labor market conditions, inflation pressures and inflation expectations, and financial and international developments.
 Voting for the monetary policy action were Jerome H. Powell, Chair; John C. Williams, Vice Chair; Michael S. Barr; Michelle W. Bowman; Lisa D. Cook; Austan D. Goolsbee; Patrick Harker; Philip N. Jefferson; Neel Kashkari; Adriana D. Kugler; Lorie K. Logan; and Christopher J. Waller.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G201" t="n">
-        <v>2428</v>
+        <v>2424</v>
       </c>
       <c r="H201" t="inlineStr"/>
     </row>
@@ -8893,7 +8893,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-08-12T20:22:22+00:00</t>
+          <t>2026-10-26T07:10:22+00:00</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -8905,11 +8905,11 @@
 The Committee seeks to achieve maximum employment and inflation at the rate of 2 percent over the longer run. In support of these goals, the Committee decided to maintain the target range for the federal funds rate at 5-1/4 to 5-1/2 percent. The Committee will continue to assess additional information and its implications for monetary policy. In determining the extent of any additional policy firming that may be appropriate to return inflation to 2 percent over time, the Committee will take into account the cumulative tightening of monetary policy, the lags with which monetary policy affects economic activity and inflation, and economic and financial developments. In addition, the Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgage-backed securities, as described in its previously announced plans. The Committee is strongly committed to returning inflation to its 2 percent objective.
 In assessing the appropriate stance of monetary policy, the Committee will continue to monitor the implications of incoming information for the economic outlook. The Committee would be prepared to adjust the stance of monetary policy as appropriate if risks emerge that could impede the attainment of the Committee's goals. The Committee's assessments will take into account a wide range of information, including readings on labor market conditions, inflation pressures and inflation expectations, and financial and international developments.
 Voting for the monetary policy action were Jerome H. Powell, Chair; John C. Williams, Vice Chair; Michael S. Barr; Michelle W. Bowman; Lisa D. Cook; Austan D. Goolsbee; Patrick Harker; Philip N. Jefferson; Neel Kashkari; Adriana D. Kugler; Lorie K. Logan; and Christopher J. Waller.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G202" t="n">
-        <v>2481</v>
+        <v>2477</v>
       </c>
       <c r="H202" t="inlineStr"/>
     </row>
@@ -8936,7 +8936,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-08-12T20:22:30+00:00</t>
+          <t>2026-10-26T07:10:23+00:00</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -8948,11 +8948,11 @@
 In support of its goals, the Committee decided to maintain the target range for the federal funds rate at 5-1/4 to 5-1/2 percent. In considering any adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee does not expect it will be appropriate to reduce the target range until it has gained greater confidence that inflation is moving sustainably toward 2 percent. In addition, the Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgage-backed securities, as described in its previously announced plans. The Committee is strongly committed to returning inflation to its 2 percent objective.
 In assessing the appropriate stance of monetary policy, the Committee will continue to monitor the implications of incoming information for the economic outlook. The Committee would be prepared to adjust the stance of monetary policy as appropriate if risks emerge that could impede the attainment of the Committee's goals. The Committee's assessments will take into account a wide range of information, including readings on labor market conditions, inflation pressures and inflation expectations, and financial and international developments.
 Voting for the monetary policy action were Jerome H. Powell, Chair; John C. Williams, Vice Chair; Thomas I. Barkin; Michael S. Barr; Raphael W. Bostic; Michelle W. Bowman; Lisa D. Cook; Mary C. Daly; Philip N. Jefferson; Adriana D. Kugler; Loretta J. Mester; and Christopher J. Waller.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G203" t="n">
-        <v>2295</v>
+        <v>2291</v>
       </c>
       <c r="H203" t="inlineStr"/>
     </row>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-08-12T20:22:37+00:00</t>
+          <t>2026-10-26T07:10:24+00:00</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -8991,11 +8991,11 @@
 In support of its goals, the Committee decided to maintain the target range for the federal funds rate at 5-1/4 to 5-1/2 percent. In considering any adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee does not expect it will be appropriate to reduce the target range until it has gained greater confidence that inflation is moving sustainably toward 2 percent. In addition, the Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgage-backed securities, as described in its previously announced plans. The Committee is strongly committed to returning inflation to its 2 percent objective.
 In assessing the appropriate stance of monetary policy, the Committee will continue to monitor the implications of incoming information for the economic outlook. The Committee would be prepared to adjust the stance of monetary policy as appropriate if risks emerge that could impede the attainment of the Committee's goals. The Committee's assessments will take into account a wide range of information, including readings on labor market conditions, inflation pressures and inflation expectations, and financial and international developments.
 Voting for the monetary policy action were Jerome H. Powell, Chair; John C. Williams, Vice Chair; Thomas I. Barkin; Michael S. Barr; Raphael W. Bostic; Michelle W. Bowman; Lisa D. Cook; Mary C. Daly; Philip N. Jefferson; Adriana D. Kugler; Loretta J. Mester; and Christopher J. Waller.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G204" t="n">
-        <v>2259</v>
+        <v>2255</v>
       </c>
       <c r="H204" t="inlineStr"/>
     </row>
@@ -9022,7 +9022,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-08-12T20:22:45+00:00</t>
+          <t>2026-10-26T07:10:25+00:00</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -9031,14 +9031,14 @@
 For release at 2:00 p.m. EDT
 Recent indicators suggest that economic activity has continued to expand at a solid pace. Job gains have remained strong, and the unemployment rate has remained low. Inflation has eased over the past year but remains elevated. In recent months, there has been a lack of further progress toward the Committee's 2 percent inflation objective.
 The Committee seeks to achieve maximum employment and inflation at the rate of 2 percent over the longer run. The Committee judges that the risks to achieving its employment and inflation goals have moved toward better balance over the past year. The economic outlook is uncertain, and the Committee remains highly attentive to inflation risks.
-In support of its goals, the Committee decided to maintain the target range for the federal funds rate at 5-1/4 to 5-1/2 percent. In considering any adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee does not expect it will be appropriate to reduce the target range until it has gained greater confidence that inflation is moving sustainably toward 2 percent. In addition, the Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgageâbacked securities. Beginning in June, the Committee will slow the pace of decline of its securities holdings by reducing the monthly redemption cap on Treasury securities from $60 billion to $25 billion. The Committee will maintain the monthly redemption cap on agency debt and agency mortgageâbacked securities at $35 billion and will reinvest any principal payments in excess of this cap into Treasury securities. The Committee is strongly committed to returning inflation to its 2 percent objective.
+In support of its goals, the Committee decided to maintain the target range for the federal funds rate at 5-1/4 to 5-1/2 percent. In considering any adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee does not expect it will be appropriate to reduce the target range until it has gained greater confidence that inflation is moving sustainably toward 2 percent. In addition, the Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgage‑backed securities. Beginning in June, the Committee will slow the pace of decline of its securities holdings by reducing the monthly redemption cap on Treasury securities from $60 billion to $25 billion. The Committee will maintain the monthly redemption cap on agency debt and agency mortgage‑backed securities at $35 billion and will reinvest any principal payments in excess of this cap into Treasury securities. The Committee is strongly committed to returning inflation to its 2 percent objective.
 In assessing the appropriate stance of monetary policy, the Committee will continue to monitor the implications of incoming information for the economic outlook. The Committee would be prepared to adjust the stance of monetary policy as appropriate if risks emerge that could impede the attainment of the Committee's goals. The Committee's assessments will take into account a wide range of information, including readings on labor market conditions, inflation pressures and inflation expectations, and financial and international developments.
 Voting for the monetary policy action were Jerome H. Powell, Chair; John C. Williams, Vice Chair; Thomas I. Barkin; Michael S. Barr; Raphael W. Bostic; Michelle W. Bowman; Lisa D. Cook; Mary C. Daly; Philip N. Jefferson; Adriana D. Kugler; Loretta J. Mester; and Christopher J. Waller.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G205" t="n">
-        <v>2750</v>
+        <v>2742</v>
       </c>
       <c r="H205" t="inlineStr"/>
     </row>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-08-12T20:22:53+00:00</t>
+          <t>2026-10-26T07:10:26+00:00</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -9074,14 +9074,14 @@
 For release at 2:00 p.m. EDT
 Recent indicators suggest that economic activity has continued to expand at a solid pace. Job gains have remained strong, and the unemployment rate has remained low. Inflation has eased over the past year but remains elevated. In recent months, there has been modest further progress toward the Committee's 2 percent inflation objective.
 The Committee seeks to achieve maximum employment and inflation at the rate of 2 percent over the longer run. The Committee judges that the risks to achieving its employment and inflation goals have moved toward better balance over the past year. The economic outlook is uncertain, and the Committee remains highly attentive to inflation risks.
-In support of its goals, the Committee decided to maintain the target range for the federal funds rate at 5-1/4 to 5-1/2 percent. In considering any adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee does not expect it will be appropriate to reduce the target range until it has gained greater confidence that inflation is moving sustainably toward 2 percent. In addition, the Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgageâbacked securities. The Committee is strongly committed to returning inflation to its 2 percent objective.
+In support of its goals, the Committee decided to maintain the target range for the federal funds rate at 5-1/4 to 5-1/2 percent. In considering any adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee does not expect it will be appropriate to reduce the target range until it has gained greater confidence that inflation is moving sustainably toward 2 percent. In addition, the Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgage‑backed securities. The Committee is strongly committed to returning inflation to its 2 percent objective.
 In assessing the appropriate stance of monetary policy, the Committee will continue to monitor the implications of incoming information for the economic outlook. The Committee would be prepared to adjust the stance of monetary policy as appropriate if risks emerge that could impede the attainment of the Committee's goals. The Committee's assessments will take into account a wide range of information, including readings on labor market conditions, inflation pressures and inflation expectations, and financial and international developments.
 Voting for the monetary policy action were Jerome H. Powell, Chair; John C. Williams, Vice Chair; Thomas I. Barkin; Michael S. Barr; Raphael W. Bostic; Michelle W. Bowman; Lisa D. Cook; Mary C. Daly; Philip N. Jefferson; Adriana D. Kugler; Loretta J. Mester; and Christopher J. Waller.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G206" t="n">
-        <v>2349</v>
+        <v>2343</v>
       </c>
       <c r="H206" t="inlineStr"/>
     </row>
@@ -9108,7 +9108,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-08-12T20:23:01+00:00</t>
+          <t>2026-10-26T07:10:27+00:00</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -9117,14 +9117,14 @@
 For release at 2:00 p.m. EDT
 Recent indicators suggest that economic activity has continued to expand at a solid pace. Job gains have moderated, and the unemployment rate has moved up but remains low. Inflation has eased over the past year but remains somewhat elevated. In recent months, there has been some further progress toward the Committee's 2 percent inflation objective.
 The Committee seeks to achieve maximum employment and inflation at the rate of 2 percent over the longer run. The Committee judges that the risks to achieving its employment and inflation goals continue to move into better balance. The economic outlook is uncertain, and the Committee is attentive to the risks to both sides of its dual mandate.
-In support of its goals, the Committee decided to maintain the target range for the federal funds rate at 5-1/4 to 5-1/2 percent. In considering any adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee does not expect it will be appropriate to reduce the target range until it has gained greater confidence that inflation is moving sustainably toward 2 percent. In addition, the Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgageâbacked securities. The Committee is strongly committed to returning inflation to its 2 percent objective.
+In support of its goals, the Committee decided to maintain the target range for the federal funds rate at 5-1/4 to 5-1/2 percent. In considering any adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee does not expect it will be appropriate to reduce the target range until it has gained greater confidence that inflation is moving sustainably toward 2 percent. In addition, the Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgage‑backed securities. The Committee is strongly committed to returning inflation to its 2 percent objective.
 In assessing the appropriate stance of monetary policy, the Committee will continue to monitor the implications of incoming information for the economic outlook. The Committee would be prepared to adjust the stance of monetary policy as appropriate if risks emerge that could impede the attainment of the Committee's goals. The Committee's assessments will take into account a wide range of information, including readings on labor market conditions, inflation pressures and inflation expectations, and financial and international developments.
 Voting for the monetary policy action were Jerome H. Powell, Chair; John C. Williams, Vice Chair; Thomas I. Barkin; Michael S. Barr; Raphael W. Bostic; Michelle W. Bowman; Lisa D. Cook; Mary C. Daly; Austan D. Goolsbee; Philip N. Jefferson; Adriana D. Kugler; and Christopher J. Waller. Austan D. Goolsbee voted as an alternate member at this meeting.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G207" t="n">
-        <v>2429</v>
+        <v>2423</v>
       </c>
       <c r="H207" t="inlineStr"/>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-08-12T20:23:08+00:00</t>
+          <t>2026-10-26T07:10:28+00:00</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -9160,14 +9160,14 @@
 For release at 2:00 p.m. EDT
 Recent indicators suggest that economic activity has continued to expand at a solid pace. Job gains have slowed, and the unemployment rate has moved up but remains low. Inflation has made further progress toward the Committee's 2 percent objective but remains somewhat elevated.
 The Committee seeks to achieve maximum employment and inflation at the rate of 2 percent over the longer run. The Committee has gained greater confidence that inflation is moving sustainably toward 2 percent, and judges that the risks to achieving its employment and inflation goals are roughly in balance. The economic outlook is uncertain, and the Committee is attentive to the risks to both sides of its dual mandate.
-In light of the progress on inflation and the balance of risks, the Committee decided to lower the target range for the federal funds rate by 1/2 percentage point to 4-3/4 to 5 percent. In considering additional adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgageâbacked securities. The Committee is strongly committed to supporting maximum employment and returning inflation to its 2 percent objective.
+In light of the progress on inflation and the balance of risks, the Committee decided to lower the target range for the federal funds rate by 1/2 percentage point to 4-3/4 to 5 percent. In considering additional adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgage‑backed securities. The Committee is strongly committed to supporting maximum employment and returning inflation to its 2 percent objective.
 In assessing the appropriate stance of monetary policy, the Committee will continue to monitor the implications of incoming information for the economic outlook. The Committee would be prepared to adjust the stance of monetary policy as appropriate if risks emerge that could impede the attainment of the Committee's goals. The Committee's assessments will take into account a wide range of information, including readings on labor market conditions, inflation pressures and inflation expectations, and financial and international developments.
 Voting for the monetary policy action were Jerome H. Powell, Chair; John C. Williams, Vice Chair; Thomas I. Barkin; Michael S. Barr; Raphael W. Bostic; Lisa D. Cook; Mary C. Daly; Beth M. Hammack; Philip N. Jefferson; Adriana D. Kugler; and Christopher J. Waller. Voting against this action was Michelle W. Bowman, who preferred to lower the target range for the federal funds rate by 1/4 percentage point at this meeting.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G208" t="n">
-        <v>2418</v>
+        <v>2412</v>
       </c>
       <c r="H208" t="inlineStr"/>
     </row>
@@ -9194,7 +9194,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-08-12T20:23:16+00:00</t>
+          <t>2026-10-26T07:10:29+00:00</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -9203,14 +9203,14 @@
 For release at 2:00 p.m. EST
 Recent indicators suggest that economic activity has continued to expand at a solid pace. Since earlier in the year, labor market conditions have generally eased, and the unemployment rate has moved up but remains low. Inflation has made progress toward the Committee's 2 percent objective but remains somewhat elevated.
 The Committee seeks to achieve maximum employment and inflation at the rate of 2 percent over the longer run. The Committee judges that the risks to achieving its employment and inflation goals are roughly in balance. The economic outlook is uncertain, and the Committee is attentive to the risks to both sides of its dual mandate.
-In support of its goals, the Committee decided to lower the target range for the federal funds rate by 1/4 percentage point to 4-1/2 to 4-3/4 percent. In considering additional adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgageâbacked securities. The Committee is strongly committed to supporting maximum employment and returning inflation to its 2 percent objective.
+In support of its goals, the Committee decided to lower the target range for the federal funds rate by 1/4 percentage point to 4-1/2 to 4-3/4 percent. In considering additional adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgage‑backed securities. The Committee is strongly committed to supporting maximum employment and returning inflation to its 2 percent objective.
 In assessing the appropriate stance of monetary policy, the Committee will continue to monitor the implications of incoming information for the economic outlook. The Committee would be prepared to adjust the stance of monetary policy as appropriate if risks emerge that could impede the attainment of the Committee's goals. The Committee's assessments will take into account a wide range of information, including readings on labor market conditions, inflation pressures and inflation expectations, and financial and international developments.
 Voting for the monetary policy action were Jerome H. Powell, Chair; John C. Williams, Vice Chair; Thomas I. Barkin; Michael S. Barr; Raphael W. Bostic; Michelle W. Bowman; Lisa D. Cook; Mary C. Daly; Beth M. Hammack; Philip N. Jefferson; Adriana D. Kugler; and Christopher J. Waller.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G209" t="n">
-        <v>2196</v>
+        <v>2190</v>
       </c>
       <c r="H209" t="inlineStr"/>
     </row>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>2026-08-12T20:23:23+00:00</t>
+          <t>2026-10-26T07:10:30+00:00</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -9246,14 +9246,14 @@
 For release at 2:00 p.m. EST
 Recent indicators suggest that economic activity has continued to expand at a solid pace. Since earlier in the year, labor market conditions have generally eased, and the unemployment rate has moved up but remains low. Inflation has made progress toward the Committee's 2 percent objective but remains somewhat elevated.
 The Committee seeks to achieve maximum employment and inflation at the rate of 2 percent over the longer run. The Committee judges that the risks to achieving its employment and inflation goals are roughly in balance. The economic outlook is uncertain, and the Committee is attentive to the risks to both sides of its dual mandate.
-In support of its goals, the Committee decided to lower the target range for the federal funds rate by 1/4 percentage point to 4-1/4 to 4-1/2 percent. In considering the extent and timing of additional adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgageâbacked securities. The Committee is strongly committed to supporting maximum employment and returning inflation to its 2 percent objective.
+In support of its goals, the Committee decided to lower the target range for the federal funds rate by 1/4 percentage point to 4-1/4 to 4-1/2 percent. In considering the extent and timing of additional adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgage‑backed securities. The Committee is strongly committed to supporting maximum employment and returning inflation to its 2 percent objective.
 In assessing the appropriate stance of monetary policy, the Committee will continue to monitor the implications of incoming information for the economic outlook. The Committee would be prepared to adjust the stance of monetary policy as appropriate if risks emerge that could impede the attainment of the Committee's goals. The Committee's assessments will take into account a wide range of information, including readings on labor market conditions, inflation pressures and inflation expectations, and financial and international developments.
 Voting for the monetary policy action were Jerome H. Powell, Chair; John C. Williams, Vice Chair; Thomas I. Barkin; Michael S. Barr; Raphael W. Bostic; Michelle W. Bowman; Lisa D. Cook; Mary C. Daly; Philip N. Jefferson; Adriana D. Kugler; and Christopher J. Waller. Voting against the action was Beth M. Hammack, who preferred to maintain the target range for the federal funds rate at 4-1/2 to 4-3/4 percent.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G210" t="n">
-        <v>2348</v>
+        <v>2342</v>
       </c>
       <c r="H210" t="inlineStr"/>
     </row>
@@ -9280,7 +9280,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-08-12T20:23:31+00:00</t>
+          <t>2026-10-26T07:10:31+00:00</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -9289,14 +9289,14 @@
 For release at 2:00 p.m. EST
 Recent indicators suggest that economic activity has continued to expand at a solid pace. The unemployment rate has stabilized at a low level in recent months, and labor market conditions remain solid. Inflation remains somewhat elevated.
 The Committee seeks to achieve maximum employment and inflation at the rate of 2 percent over the longer run. The Committee judges that the risks to achieving its employment and inflation goals are roughly in balance. The economic outlook is uncertain, and the Committee is attentive to the risks to both sides of its dual mandate.
-In support of its goals, the Committee decided to maintain the target range for the federal funds rate at 4-1/4 to 4-1/2 percent. In considering the extent and timing of additional adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgageâbacked securities. The Committee is strongly committed to supporting maximum employment and returning inflation to its 2 percent objective.
+In support of its goals, the Committee decided to maintain the target range for the federal funds rate at 4-1/4 to 4-1/2 percent. In considering the extent and timing of additional adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgage‑backed securities. The Committee is strongly committed to supporting maximum employment and returning inflation to its 2 percent objective.
 In assessing the appropriate stance of monetary policy, the Committee will continue to monitor the implications of incoming information for the economic outlook. The Committee would be prepared to adjust the stance of monetary policy as appropriate if risks emerge that could impede the attainment of the Committee's goals. The Committee's assessments will take into account a wide range of information, including readings on labor market conditions, inflation pressures and inflation expectations, and financial and international developments.
 Voting for the monetary policy action were Jerome H. Powell, Chair; John C. Williams, Vice Chair; Michael S. Barr; Michelle W. Bowman; Susan M. Collins; Lisa D. Cook; Austan D. Goolsbee; Philip N. Jefferson; Adriana D. Kugler; Alberto G. Musalem; Jeffrey R. Schmid; and Christopher J. Waller.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G211" t="n">
-        <v>2126</v>
+        <v>2120</v>
       </c>
       <c r="H211" t="inlineStr"/>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-08-12T20:23:39+00:00</t>
+          <t>2026-10-26T07:10:32+00:00</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -9332,14 +9332,14 @@
 For release at 2:00 p.m. EDT
 Recent indicators suggest that economic activity has continued to expand at a solid pace. The unemployment rate has stabilized at a low level in recent months, and labor market conditions remain solid. Inflation remains somewhat elevated.
 The Committee seeks to achieve maximum employment and inflation at the rate of 2 percent over the longer run. Uncertainty around the economic outlook has increased. The Committee is attentive to the risks to both sides of its dual mandate.
-In support of its goals, the Committee decided to maintain the target range for the federal funds rate at 4-1/4 to 4-1/2 percent. In considering the extent and timing of additional adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgageâbacked securities. Beginning in April, the Committee will slow the pace of decline of its securities holdings by reducing the monthly redemption cap on Treasury securities from $25 billion to $5 billion. The Committee will maintain the monthly redemption cap on agency debt and agency mortgage-backed securities at $35 billion. The Committee is strongly committed to supporting maximum employment and returning inflation to its 2 percent objective.
+In support of its goals, the Committee decided to maintain the target range for the federal funds rate at 4-1/4 to 4-1/2 percent. In considering the extent and timing of additional adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgage‑backed securities. Beginning in April, the Committee will slow the pace of decline of its securities holdings by reducing the monthly redemption cap on Treasury securities from $25 billion to $5 billion. The Committee will maintain the monthly redemption cap on agency debt and agency mortgage-backed securities at $35 billion. The Committee is strongly committed to supporting maximum employment and returning inflation to its 2 percent objective.
 In assessing the appropriate stance of monetary policy, the Committee will continue to monitor the implications of incoming information for the economic outlook. The Committee would be prepared to adjust the stance of monetary policy as appropriate if risks emerge that could impede the attainment of the Committee's goals. The Committee's assessments will take into account a wide range of information, including readings on labor market conditions, inflation pressures and inflation expectations, and financial and international developments.
 Voting for the monetary policy action were Jerome H. Powell, Chair; John C. Williams, Vice Chair; Michael S. Barr; Michelle W. Bowman; Susan M. Collins; Lisa D. Cook; Austan D. Goolsbee; Philip N. Jefferson; Adriana D. Kugler; Alberto G. Musalem; and Jeffrey R. Schmid. Voting against this action was Christopher J. Waller, who supported no change for the federal funds target range but preferred to continue the current pace of decline in securities holdings.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G212" t="n">
-        <v>2509</v>
+        <v>2503</v>
       </c>
       <c r="H212" t="inlineStr"/>
     </row>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-08-12T20:23:46+00:00</t>
+          <t>2026-10-26T07:10:33+00:00</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -9375,14 +9375,14 @@
 For release at 2:00 p.m. EDT
 Although swings in net exports have affected the data, recent indicators suggest that economic activity has continued to expand at a solid pace. The unemployment rate has stabilized at a low level in recent months, and labor market conditions remain solid. Inflation remains somewhat elevated.
 The Committee seeks to achieve maximum employment and inflation at the rate of 2 percent over the longer run. Uncertainty about the economic outlook has increased further. The Committee is attentive to the risks to both sides of its dual mandate and judges that the risks of higher unemployment and higher inflation have risen.
-In support of its goals, the Committee decided to maintain the target range for the federal funds rate at 4-1/4 to 4-1/2 percent. In considering the extent and timing of additional adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgageâbacked securities. The Committee is strongly committed to supporting maximum employment and returning inflation to its 2 percent objective.
+In support of its goals, the Committee decided to maintain the target range for the federal funds rate at 4-1/4 to 4-1/2 percent. In considering the extent and timing of additional adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgage‑backed securities. The Committee is strongly committed to supporting maximum employment and returning inflation to its 2 percent objective.
 In assessing the appropriate stance of monetary policy, the Committee will continue to monitor the implications of incoming information for the economic outlook. The Committee would be prepared to adjust the stance of monetary policy as appropriate if risks emerge that could impede the attainment of the Committee's goals. The Committee's assessments will take into account a wide range of information, including readings on labor market conditions, inflation pressures and inflation expectations, and financial and international developments.
 Voting for the monetary policy action were Jerome H. Powell, Chair; John C. Williams, Vice Chair; Michael S. Barr; Michelle W. Bowman; Susan M. Collins; Lisa D. Cook; Austan D. Goolsbee; Philip N. Jefferson; Neel Kashkari; Adriana D. Kugler; Alberto G. Musalem; and Christopher J. Waller. Neel Kashkari voted as an alternate member at this meeting.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G213" t="n">
-        <v>2229</v>
+        <v>2223</v>
       </c>
       <c r="H213" t="inlineStr"/>
     </row>
@@ -9409,7 +9409,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-08-12T20:23:54+00:00</t>
+          <t>2026-10-26T07:10:34+00:00</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -9418,14 +9418,14 @@
 For release at 2:00 p.m. EDT
 Although swings in net exports have affected the data, recent indicators suggest that economic activity has continued to expand at a solid pace. The unemployment rate remains low, and labor market conditions remain solid. Inflation remains somewhat elevated.
 The Committee seeks to achieve maximum employment and inflation at the rate of 2 percent over the longer run. Uncertainty about the economic outlook has diminished but remains elevated. The Committee is attentive to the risks to both sides of its dual mandate.
-In support of its goals, the Committee decided to maintain the target range for the federal funds rate at 4-1/4 to 4-1/2 percent. In considering the extent and timing of additional adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgageâbacked securities. The Committee is strongly committed to supporting maximum employment and returning inflation to its 2 percent objective.
+In support of its goals, the Committee decided to maintain the target range for the federal funds rate at 4-1/4 to 4-1/2 percent. In considering the extent and timing of additional adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgage‑backed securities. The Committee is strongly committed to supporting maximum employment and returning inflation to its 2 percent objective.
 In assessing the appropriate stance of monetary policy, the Committee will continue to monitor the implications of incoming information for the economic outlook. The Committee would be prepared to adjust the stance of monetary policy as appropriate if risks emerge that could impede the attainment of the Committee's goals. The Committee's assessments will take into account a wide range of information, including readings on labor market conditions, inflation pressures and inflation expectations, and financial and international developments.
 Voting for the monetary policy action were Jerome H. Powell, Chair; John C. Williams, Vice Chair; Michael S. Barr; Michelle W. Bowman; Susan M. Collins; Lisa D. Cook; Austan D. Goolsbee; Philip N. Jefferson; Adriana D. Kugler; Alberto G. Musalem; Jeffrey R. Schmid; and Christopher J. Waller.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G214" t="n">
-        <v>2072</v>
+        <v>2066</v>
       </c>
       <c r="H214" t="inlineStr"/>
     </row>
@@ -9452,7 +9452,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-08-12T20:24:01+00:00</t>
+          <t>2026-10-26T07:10:35+00:00</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -9461,14 +9461,14 @@
 For release at 2:00 p.m. EDT
 Although swings in net exports continue to affect the data, recent indicators suggest that growth of economic activity moderated in the first half of the year. The unemployment rate remains low, and labor market conditions remain solid. Inflation remains somewhat elevated.
 The Committee seeks to achieve maximum employment and inflation at the rate of 2 percent over the longer run. Uncertainty about the economic outlook remains elevated. The Committee is attentive to the risks to both sides of its dual mandate.
-In support of its goals, the Committee decided to maintain the target range for the federal funds rate at 4-1/4 to 4-1/2 percent. In considering the extent and timing of additional adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgageâbacked securities. The Committee is strongly committed to supporting maximum employment and returning inflation to its 2 percent objective.
+In support of its goals, the Committee decided to maintain the target range for the federal funds rate at 4-1/4 to 4-1/2 percent. In considering the extent and timing of additional adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgage‑backed securities. The Committee is strongly committed to supporting maximum employment and returning inflation to its 2 percent objective.
 In assessing the appropriate stance of monetary policy, the Committee will continue to monitor the implications of incoming information for the economic outlook. The Committee would be prepared to adjust the stance of monetary policy as appropriate if risks emerge that could impede the attainment of the Committee's goals. The Committee's assessments will take into account a wide range of information, including readings on labor market conditions, inflation pressures and inflation expectations, and financial and international developments.
 Voting for the monetary policy action were Jerome H. Powell, Chair; John C. Williams, Vice Chair; Michael S. Barr; Susan M. Collins; Lisa D. Cook; Austan D. Goolsbee; Philip N. Jefferson; Alberto G. Musalem; and Jeffrey R. Schmid. Voting against this action were Michelle W. Bowman and Christopher J. Waller, who preferred to lower the target range for the federal funds rate by 1/4 percentage point at this meeting. Absent and not voting was Adriana D. Kugler.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G215" t="n">
-        <v>2237</v>
+        <v>2231</v>
       </c>
       <c r="H215" t="inlineStr"/>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-08-12T20:24:08+00:00</t>
+          <t>2026-10-26T07:10:36+00:00</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -9504,14 +9504,14 @@
 For release at 2:00 p.m. EDT
 Recent indicators suggest that growth of economic activity moderated in the first half of the year. Job gains have slowed, and the unemployment rate has edged up but remains low. Inflation has moved up and remains somewhat elevated.
 The Committee seeks to achieve maximum employment and inflation at the rate of 2 percent over the longer run. Uncertainty about the economic outlook remains elevated. The Committee is attentive to the risks to both sides of its dual mandate and judges that downside risks to employment have risen.
-In support of its goals and in light of the shift in the balance of risks, the Committee decided to lower the target range for the federal funds rate by 1/4 percentage point to 4 to 4â1/4 percent. In considering additional adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgageâbacked securities. The Committee is strongly committed to supporting maximum employment and returning inflation to its 2 percent objective.
+In support of its goals and in light of the shift in the balance of risks, the Committee decided to lower the target range for the federal funds rate by 1/4 percentage point to 4 to 4‑1/4 percent. In considering additional adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee will continue reducing its holdings of Treasury securities and agency debt and agency mortgage‑backed securities. The Committee is strongly committed to supporting maximum employment and returning inflation to its 2 percent objective.
 In assessing the appropriate stance of monetary policy, the Committee will continue to monitor the implications of incoming information for the economic outlook. The Committee would be prepared to adjust the stance of monetary policy as appropriate if risks emerge that could impede the attainment of the Committee's goals. The Committee's assessments will take into account a wide range of information, including readings on labor market conditions, inflation pressures and inflation expectations, and financial and international developments.
 Voting for the monetary policy action were Jerome H. Powell, Chair; John C. Williams, Vice Chair; Michael S. Barr; Michelle W. Bowman; Susan M. Collins; Lisa D. Cook; Austan D. Goolsbee; Philip N. Jefferson; Alberto G. Musalem; Jeffrey R. Schmid; and Christopher J. Waller. Voting against this action was Stephen I. Miran, who preferred to lower the target range for the federal funds rate by 1/2 percentage point at this meeting.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G216" t="n">
-        <v>2270</v>
+        <v>2262</v>
       </c>
       <c r="H216" t="inlineStr"/>
     </row>
@@ -9538,7 +9538,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-08-12T20:24:16+00:00</t>
+          <t>2026-10-26T07:10:37+00:00</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -9550,11 +9550,11 @@
 In support of its goals and in light of the shift in the balance of risks, the Committee decided to lower the target range for the federal funds rate by 1/4 percentage point to 3-3/4 to 4 percent. In considering additional adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee decided to conclude the reduction of its aggregate securities holdings on December 1. The Committee is strongly committed to supporting maximum employment and returning inflation to its 2 percent objective.
 In assessing the appropriate stance of monetary policy, the Committee will continue to monitor the implications of incoming information for the economic outlook. The Committee would be prepared to adjust the stance of monetary policy as appropriate if risks emerge that could impede the attainment of the Committee's goals. The Committee's assessments will take into account a wide range of information, including readings on labor market conditions, inflation pressures and inflation expectations, and financial and international developments.
 Voting for the monetary policy action were Jerome H. Powell, Chair; John C. Williams, Vice Chair; Michael S. Barr; Michelle W. Bowman; Susan M. Collins; Lisa D. Cook; Austan D. Goolsbee; Philip N. Jefferson; Alberto G. Musalem; and Christopher J. Waller. Voting against this action were Stephen I. Miran, who preferred to lower the target range for the federal funds rate by 1/2 percentage point at this meeting, and Jeffrey R. Schmid, who preferred no change to the target range for the federal funds rate at this meeting.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G217" t="n">
-        <v>2446</v>
+        <v>2442</v>
       </c>
       <c r="H217" t="inlineStr"/>
     </row>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-08-12T20:24:24+00:00</t>
+          <t>2026-10-26T07:10:38+00:00</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -9590,15 +9590,15 @@
 For release at 2:00 p.m. EST
 Available indicators suggest that economic activity has been expanding at a moderate pace. Job gains have slowed this year, and the unemployment rate has edged up through September. More recent indicators are consistent with these developments. Inflation has moved up since earlier in the year and remains somewhat elevated.
 The Committee seeks to achieve maximum employment and inflation at the rate of 2 percent over the longer run. Uncertainty about the economic outlook remains elevated. The Committee is attentive to the risks to both sides of its dual mandate and judges that downside risks to employment rose in recent months.
-In support of its goals and in light of the shift in the balance of risks, the Committee decided to lower the target range for the federal funds rate by 1/4 percentage point to 3-1/2 to 3â3/4 percent. In considering the extent and timing of additional adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee is strongly committed to supporting maximum employment and returning inflation to its 2 percent objective.
+In support of its goals and in light of the shift in the balance of risks, the Committee decided to lower the target range for the federal funds rate by 1/4 percentage point to 3-1/2 to 3‑3/4 percent. In considering the extent and timing of additional adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee is strongly committed to supporting maximum employment and returning inflation to its 2 percent objective.
 In assessing the appropriate stance of monetary policy, the Committee will continue to monitor the implications of incoming information for the economic outlook. The Committee would be prepared to adjust the stance of monetary policy as appropriate if risks emerge that could impede the attainment of the Committee's goals. The Committee's assessments will take into account a wide range of information, including readings on labor market conditions, inflation pressures and inflation expectations, and financial and international developments.
 The Committee judges that reserve balances have declined to ample levels and will initiate purchases of shorter-term Treasury securities as needed to maintain an ample supply of reserves on an ongoing basis.
 Voting for the monetary policy action were Jerome H. Powell, Chair; John C. Williams, Vice Chair; Michael S. Barr; Michelle W. Bowman; Susan M. Collins; Lisa D. Cook; Philip N. Jefferson; Alberto G. Musalem; and Christopher J. Waller. Voting against this action were Stephen I. Miran, who preferred to lower the target range for the federal funds rate by 1/2 percentage point at this meeting; and Austan D. Goolsbee and Jeffrey R. Schmid, who preferred no change to the target range for the federal funds rate at this meeting.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G218" t="n">
-        <v>2576</v>
+        <v>2570</v>
       </c>
       <c r="H218" t="inlineStr"/>
     </row>
@@ -9625,7 +9625,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-08-12T20:24:31+00:00</t>
+          <t>2026-10-26T07:10:39+00:00</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -9634,14 +9634,14 @@
 For release at 2:00 p.m. EST
 Available indicators suggest that economic activity has been expanding at a solid pace. Job gains have remained low, and the unemployment rate has shown some signs of stabilization. Inflation remains somewhat elevated.
 The Committee seeks to achieve maximum employment and inflation at the rate of 2 percent over the longer run. Uncertainty about the economic outlook remains elevated. The Committee is attentive to the risks to both sides of its dual mandate.
-In support of its goals, the Committee decided to maintain the target range for the federal funds rate at 3â1/2 to 3â3/4 percent. In considering the extent and timing of additional adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee is strongly committed to supporting maximum employment and returning inflation to its 2 percent objective.
+In support of its goals, the Committee decided to maintain the target range for the federal funds rate at 3‑1/2 to 3‑3/4 percent. In considering the extent and timing of additional adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee is strongly committed to supporting maximum employment and returning inflation to its 2 percent objective.
 In assessing the appropriate stance of monetary policy, the Committee will continue to monitor the implications of incoming information for the economic outlook. The Committee would be prepared to adjust the stance of monetary policy as appropriate if risks emerge that could impede the attainment of the Committee's goals. The Committee's assessments will take into account a wide range of information, including readings on labor market conditions, inflation pressures and inflation expectations, and financial and international developments.
 Voting for the monetary policy action were Jerome H. Powell, Chair; John C. Williams, Vice Chair; Michael S. Barr; Michelle W. Bowman; Lisa D. Cook; Beth M. Hammack; Philip N. Jefferson; Neel Kashkari; Lorie K. Logan; and Anna Paulson. Voting against this action were Stephen I. Miran and Christopher J. Waller, who preferred to lower the target range for the federal funds rate by 1/4 percentage point at this meeting.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G219" t="n">
-        <v>2017</v>
+        <v>2009</v>
       </c>
       <c r="H219" t="inlineStr"/>
     </row>
@@ -9668,7 +9668,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-08-12T20:24:39+00:00</t>
+          <t>2026-10-26T07:10:40+00:00</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -9677,14 +9677,14 @@
 For release at 2:00 p.m. EDT
 Available indicators suggest that economic activity has been expanding at a solid pace. Job gains have remained low, and the unemployment rate has been little changed in recent months. Inflation remains somewhat elevated.
 The Committee seeks to achieve maximum employment and inflation at the rate of 2 percent over the longer run. Uncertainty about the economic outlook remains elevated. The implications of developments in the Middle East for the U.S. economy are uncertain. The Committee is attentive to the risks to both sides of its dual mandate.
-In support of its goals, the Committee decided to maintain the target range for the federal funds rate at 3â1/2 to 3â3/4 percent. In considering the extent and timing of additional adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee is strongly committed to supporting maximum employment and returning inflation to its 2 percent objective.
+In support of its goals, the Committee decided to maintain the target range for the federal funds rate at 3‑1/2 to 3‑3/4 percent. In considering the extent and timing of additional adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee is strongly committed to supporting maximum employment and returning inflation to its 2 percent objective.
 In assessing the appropriate stance of monetary policy, the Committee will continue to monitor the implications of incoming information for the economic outlook. The Committee would be prepared to adjust the stance of monetary policy as appropriate if risks emerge that could impede the attainment of the Committee's goals. The Committee's assessments will take into account a wide range of information, including readings on labor market conditions, inflation pressures and inflation expectations, and financial and international developments.
 Voting for the monetary policy action were Jerome H. Powell, Chair; John C. Williams, Vice Chair; Michael S. Barr; Michelle W. Bowman; Lisa D. Cook; Beth M. Hammack; Philip N. Jefferson; Neel Kashkari; Lorie K. Logan; Anna Paulson; and Christopher J. Waller. Voting against this action was Stephen I. Miran, who preferred to lower the target range for the federal funds rate by 1/4 percentage point at this meeting.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G220" t="n">
-        <v>2102</v>
+        <v>2094</v>
       </c>
       <c r="H220" t="inlineStr"/>
     </row>
@@ -9711,7 +9711,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-08-12T20:24:46+00:00</t>
+          <t>2026-10-26T07:10:41+00:00</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -9720,14 +9720,14 @@
 For release at 2:00 p.m. EDT
 Recent indicators suggest that economic activity has been expanding at a solid pace. Job gains have remained low, on average, and the unemployment rate has been little changed in recent months. Inflation is elevated, in part reflecting the recent increase in global energy prices.
 The Committee seeks to achieve maximum employment and inflation at the rate of 2 percent over the longer run. Developments in the Middle East are contributing to a high level of uncertainty about the economic outlook. The Committee is attentive to the risks to both sides of its dual mandate.
-In support of its goals, the Committee decided to maintain the target range for the federal funds rate at 3â1/2 to 3â3/4 percent. In considering the extent and timing of additional adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee is strongly committed to supporting maximum employment and returning inflation to its 2 percent objective.
+In support of its goals, the Committee decided to maintain the target range for the federal funds rate at 3‑1/2 to 3‑3/4 percent. In considering the extent and timing of additional adjustments to the target range for the federal funds rate, the Committee will carefully assess incoming data, the evolving outlook, and the balance of risks. The Committee is strongly committed to supporting maximum employment and returning inflation to its 2 percent objective.
 In assessing the appropriate stance of monetary policy, the Committee will continue to monitor the implications of incoming information for the economic outlook. The Committee would be prepared to adjust the stance of monetary policy as appropriate if risks emerge that could impede the attainment of the Committee's goals. The Committee's assessments will take into account a wide range of information, including readings on labor market conditions, inflation pressures and inflation expectations, and financial and international developments.
 Voting for the monetary policy action were Jerome H. Powell, Chair; John C. Williams, Vice Chair; Michael S. Barr; Michelle W. Bowman; Lisa D. Cook; Philip N. Jefferson; Anna Paulson; and Christopher J. Waller. Voting against this action were Stephen I. Miran, who preferred to lower the target range for the federal funds rate by 1/4 percentage point at this meeting; and Beth M. Hammack, Neel Kashkari, and Lorie K. Logan, who supported maintaining the target range for the federal funds rate but did not support inclusion of an easing bias in the statement at this time.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G221" t="n">
-        <v>2282</v>
+        <v>2274</v>
       </c>
       <c r="H221" t="inlineStr"/>
     </row>
@@ -9754,22 +9754,22 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-08-12T20:24:54+00:00</t>
+          <t>2026-10-26T07:10:42+00:00</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
           <t>June 17, 2026
 For release at 2:00 p.m. EDT
-The Federal Open Market Committee approved the following statement for release by a 12 â 0 vote:
+The Federal Open Market Committee approved the following statement for release by a 12 – 0 vote:
 The Committee decided to maintain the target range for the federal funds rate at 3-1/2 to 3-3/4 percent, in support of the Federal Reserve's dual mandate. The Committee reaffirmed its policy of maintaining ample reserves in the banking system.
 Economic activity is expanding at a solid pace despite elevated uncertainty that owes, in part, to the conflict in the Middle East. Productivity growth and capital investment are strong. Job gains have kept pace with the workforce, and the unemployment rate has changed little.
 Inflation remains elevated relative to the Committee's 2 percent goal, in part reflecting supply shocks that have driven price increases in certain sectors, including energy. The Committee will deliver price stability.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G222" t="n">
-        <v>962</v>
+        <v>956</v>
       </c>
       <c r="H222" t="inlineStr"/>
     </row>
@@ -9796,25 +9796,67 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-08-12T20:25:01+00:00</t>
+          <t>2026-10-26T07:10:43+00:00</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
           <t>July 29, 2026
 For release at 2:00 p.m. EDT
-The Federal Open Market Committee approved the following statement for release by a 9 â 3 vote:
+The Federal Open Market Committee approved the following statement for release by a 9 – 3 vote:
 The Committee decided to maintain the target range for the federal funds rate at 3-1/2 to 3-3/4 percent, in support of the Federal Reserve's dual mandate. The Committee is continuing its policy of maintaining ample reserves in the banking system.
 Economic activity is expanding at a solid pace despite elevated uncertainty that owes, in part, to the conflict in the Middle East. Productivity growth and capital investment are strong. Job gains have kept pace with the workforce, and the unemployment rate has changed little.
 Inflation remains elevated relative to the Committee's 2 percent goal, in part reflecting supply shocks that have driven price increases in certain sectors, including energy. The Committee will deliver price stability.
 Voting against the monetary policy action were Beth M. Hammack, Neel Kashkari, and Lorie K. Logan, who preferred to raise the target range for the federal funds rate by 1/4 percentage point at this meeting.
-For media inquiries, please email [email protected] or call 202-452-2955.</t>
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
         </is>
       </c>
       <c r="G223" t="n">
-        <v>1172</v>
+        <v>1166</v>
       </c>
       <c r="H223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>https://www.federalreserve.gov/newsevents/pressreleases/monetary20260916a.htm</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>2026-10-26T07:10:45+00:00</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>September 16, 2026
+For release at 2:00 p.m. EDT
+The Federal Open Market Committee approved the following statement for release by a 12 – 0 vote:
+The Committee decided to raise the target range for the federal funds rate by 1/4 percentage point to 3-3/4 to 4 percent, in support of the Federal Reserve's dual mandate. The Committee is continuing its policy of maintaining ample reserves in the banking system.
+Economic activity is expanding at a solid pace. While uncertainty remains elevated owing, in part, to geopolitical developments, domestic spending has been resilient. Productivity growth is strong, and capital investment is robust. Job gains have kept pace with the workforce, and the unemployment rate has changed little.
+Inflation remains elevated. Today's policy action will support a timelier return to the Committee's 2 percent goal. The Committee will deliver price stability.
+For media inquiries, please email media@frb.gov or call 202-452-2955.</t>
+        </is>
+      </c>
+      <c r="G224" t="n">
+        <v>967</v>
+      </c>
+      <c r="H224" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
